--- a/xlsx/DSA.xlsx
+++ b/xlsx/DSA.xlsx
@@ -12,14 +12,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="zgBtyc52RW3pq3g5WVPu9vEK7NIet2xdPbbtO5JYpuY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="/5v9k1KJiP+4A5dbTlMiRay+RX6x3V235JJyH2nd5fk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="311">
   <si>
     <t>PROBLEM NAME</t>
   </si>
@@ -42,6 +42,12 @@
     <t>Valid Parentheses</t>
   </si>
   <si>
+    <t>Implement Queue using Stacks</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/implement-queue-using-stacks/</t>
+  </si>
+  <si>
     <t>Reverse Linked List</t>
   </si>
   <si>
@@ -51,15 +57,45 @@
     <t>https://leetcode.com/problems/reverse-linked-list/</t>
   </si>
   <si>
-    <t>Implement Queue using Stacks</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/implement-queue-using-stacks/</t>
+    <t>Maximum Sum / Average Subarray</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/maximum-average-subarray-i/description/</t>
   </si>
   <si>
     <t>EASY</t>
   </si>
   <si>
+    <t>Simulation</t>
+  </si>
+  <si>
+    <t>Stack Matching</t>
+  </si>
+  <si>
+    <t>Queue/Stack</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Amazon, Google</t>
+  </si>
+  <si>
+    <t>Number of Recent Calls</t>
+  </si>
+  <si>
+    <t>Min Stack</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/number-of-recent-calls/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/min-stack/</t>
+  </si>
+  <si>
     <t>Iteration / Pointer Manipulation</t>
   </si>
   <si>
@@ -69,94 +105,124 @@
     <t>Amazon, Google, Microsoft, Apple</t>
   </si>
   <si>
-    <t>Stack Matching</t>
-  </si>
-  <si>
-    <t>Simulation</t>
-  </si>
-  <si>
-    <t>Queue/Stack</t>
-  </si>
-  <si>
-    <t>Stack</t>
-  </si>
-  <si>
     <t>Find Middle of Linked List</t>
   </si>
   <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Amazon, Google</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/middle-of-the-linked-list/</t>
   </si>
   <si>
-    <t>Number of Recent Calls</t>
-  </si>
-  <si>
-    <t>Min Stack</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/min-stack/</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/number-of-recent-calls/</t>
+    <t>Sliding window(Fixed)</t>
+  </si>
+  <si>
+    <t>Sliding Window</t>
+  </si>
+  <si>
+    <t>Queue</t>
+  </si>
+  <si>
+    <t>Array</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Design + Stack</t>
+  </si>
+  <si>
+    <t>Amazon, Google, Microsoft</t>
+  </si>
+  <si>
+    <t>Moving Average from Data Stream</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/moving-average-from-data-stream/</t>
+  </si>
+  <si>
+    <t>Implement Stack using Queues</t>
+  </si>
+  <si>
+    <t>Minimum Size Subarray Sum</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/implement-stack-using-queues/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/minimum-size-subarray-sum/</t>
   </si>
   <si>
     <t>Fast &amp; Slow Pointer</t>
   </si>
   <si>
-    <t>Sliding Window</t>
-  </si>
-  <si>
     <t>Meta, Amazon, Goldman Sachs</t>
   </si>
   <si>
-    <t>Queue</t>
-  </si>
-  <si>
-    <t>Design + Stack</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
     <t>Detect Cycle in Linked List (Floyd’s Algorithm)</t>
   </si>
   <si>
-    <t>Moving Average from Data Stream</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/linked-list-cycle/</t>
   </si>
   <si>
-    <t>https://leetcode.com/problems/moving-average-from-data-stream/</t>
-  </si>
-  <si>
-    <t>Implement Stack using Queues</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/implement-stack-using-queues/</t>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>Stack/Queue</t>
+  </si>
+  <si>
+    <t>First Unique Character in String</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/first-unique-character-in-a-string/</t>
+  </si>
+  <si>
+    <t>Baseball Game</t>
+  </si>
+  <si>
+    <t>Stack Simulation</t>
+  </si>
+  <si>
+    <t>Backspace String Compare</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/backspace-string-compare/</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>Sliding Window (Variable)</t>
+  </si>
+  <si>
+    <t>Amazon, Meta</t>
+  </si>
+  <si>
+    <t>Queue + HashMap</t>
+  </si>
+  <si>
+    <t>Subarray Sum Equals K</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/subarray-sum-equals-k/</t>
+  </si>
+  <si>
+    <t>Design Circular Queue</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/design-circular-queue/</t>
   </si>
   <si>
     <t>Fast &amp; Slow Pointer (Cycle Detection)</t>
   </si>
   <si>
-    <t>Facebook</t>
+    <t>Stack / Two Pointer</t>
   </si>
   <si>
     <t>Google, Amazon, JPMorgan</t>
   </si>
   <si>
-    <t>First Unique Character in String</t>
-  </si>
-  <si>
-    <t>Maximum Sum / Average Subarray</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/first-unique-character-in-a-string/</t>
+    <t>Remove Outermost Parentheses</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/remove-outermost-parentheses/</t>
   </si>
   <si>
     <t>Merge Two Sorted Linked Lists</t>
@@ -165,31 +231,22 @@
     <t>https://leetcode.com/problems/merge-two-sorted-lists/</t>
   </si>
   <si>
-    <t>https://leetcode.com/problems/maximum-average-subarray-i/description/</t>
-  </si>
-  <si>
-    <t>Stack/Queue</t>
-  </si>
-  <si>
-    <t>Baseball Game</t>
-  </si>
-  <si>
-    <t>Stack Simulation</t>
-  </si>
-  <si>
-    <t>Backspace String Compare</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/backspace-string-compare/</t>
-  </si>
-  <si>
-    <t>Queue + HashMap</t>
-  </si>
-  <si>
-    <t>Design Circular Queue</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/design-circular-queue/</t>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Time Needed to Buy Tickets</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/time-needed-to-buy-tickets/</t>
+  </si>
+  <si>
+    <t>Make The String Great</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/make-the-string-great/</t>
   </si>
   <si>
     <t>Two Pointer Merge</t>
@@ -204,40 +261,34 @@
     <t>https://leetcode.com/problems/remove-duplicates-from-sorted-list/</t>
   </si>
   <si>
-    <t>Sliding window(Fixed)</t>
-  </si>
-  <si>
-    <t>Stack / Two Pointer</t>
-  </si>
-  <si>
-    <t>Array</t>
-  </si>
-  <si>
-    <t>Design</t>
-  </si>
-  <si>
-    <t>Amazon, Google, Microsoft</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>Time Needed to Buy Tickets</t>
-  </si>
-  <si>
-    <t>Minimum Size Subarray Sum</t>
-  </si>
-  <si>
-    <t>Remove Outermost Parentheses</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/time-needed-to-buy-tickets/</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/minimum-size-subarray-sum/</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/remove-outermost-parentheses/</t>
+    <t>Implement Stack using Queue</t>
+  </si>
+  <si>
+    <t>Prefix Sum + Sliding Window Concept</t>
+  </si>
+  <si>
+    <t>Array + HashMap</t>
+  </si>
+  <si>
+    <t>Meta, Amazon</t>
+  </si>
+  <si>
+    <t>Crawler Log Folder</t>
+  </si>
+  <si>
+    <t>Subarray Sums Divisible by K</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/crawler-log-folder/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/subarray-sums-divisible-by-k/</t>
+  </si>
+  <si>
+    <t>Dota2 Senate</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/dota2-senate/</t>
   </si>
   <si>
     <t>Two Pointer</t>
@@ -246,34 +297,40 @@
     <t>Amazon, Apple</t>
   </si>
   <si>
+    <t>Build an Array With Stack Operations</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/build-an-array-with-stack-operations/</t>
+  </si>
+  <si>
     <t>Delete Node Given Only That Node</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/delete-node-in-a-linked-list/</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>Sliding Window (Variable)</t>
-  </si>
-  <si>
-    <t>Amazon, Meta</t>
-  </si>
-  <si>
-    <t>Subarray Sum Equals K</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/subarray-sum-equals-k/</t>
-  </si>
-  <si>
-    <t>Implement Stack using Queue</t>
-  </si>
-  <si>
-    <t>Make The String Great</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/make-the-string-great/</t>
+    <t>Queue Simulation</t>
+  </si>
+  <si>
+    <t>Number of Students Unable to Eat Lunch</t>
+  </si>
+  <si>
+    <t>Prefix Sum (Sliding Window Variant)</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/number-of-students-unable-to-eat-lunch/</t>
+  </si>
+  <si>
+    <t>Sliding Window Maximum</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/sliding-window-maximum/</t>
+  </si>
+  <si>
+    <t>Final Prices With Discount</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/final-prices-with-a-special-discount-in-a-shop/</t>
   </si>
   <si>
     <t>Trick / In-place Overwrite</t>
@@ -282,37 +339,40 @@
     <t>Google, Meta</t>
   </si>
   <si>
-    <t>Prefix Sum + Sliding Window Concept</t>
-  </si>
-  <si>
     <t>Remove Elements (Delete all nodes with given value)</t>
   </si>
   <si>
-    <t>Array + HashMap</t>
-  </si>
-  <si>
-    <t>Meta, Amazon</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/remove-linked-list-elements/</t>
   </si>
   <si>
-    <t>Subarray Sums Divisible by K</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/subarray-sums-divisible-by-k/</t>
-  </si>
-  <si>
-    <t>Dota2 Senate</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/dota2-senate/</t>
-  </si>
-  <si>
-    <t>Crawler Log Folder</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/crawler-log-folder/</t>
+    <t>Monotonic Stack</t>
+  </si>
+  <si>
+    <t>Remove All Adjacent Duplicates</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/remove-all-adjacent-duplicates-in-string/</t>
+  </si>
+  <si>
+    <t>Design Circular Deque</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/design-circular-deque/</t>
+  </si>
+  <si>
+    <t>HARD</t>
+  </si>
+  <si>
+    <t>Monotonic Deque</t>
+  </si>
+  <si>
+    <t>Deque</t>
+  </si>
+  <si>
+    <t>Subarrays with K Different Integers</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/subarrays-with-k-different-integers/</t>
   </si>
   <si>
     <t>Iteration / Dummy Node</t>
@@ -321,100 +381,88 @@
     <t>Amazon, Goldman Sachs</t>
   </si>
   <si>
-    <t>Prefix Sum (Sliding Window Variant)</t>
-  </si>
-  <si>
     <t>Linked List Length / Size</t>
   </si>
   <si>
-    <t>Queue Simulation</t>
-  </si>
-  <si>
     <t>https://www.hackerrank.com/challenges/get-the-value-of-the-node-at-a-specific-position-from-the-tail/problem</t>
   </si>
   <si>
-    <t>Sliding Window Maximum</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/sliding-window-maximum/</t>
-  </si>
-  <si>
-    <t>Number of Students Unable to Eat Lunch</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/number-of-students-unable-to-eat-lunch/</t>
-  </si>
-  <si>
-    <t>HARD</t>
-  </si>
-  <si>
-    <t>Monotonic Deque</t>
-  </si>
-  <si>
-    <t>Deque</t>
-  </si>
-  <si>
-    <t>Subarrays with K Different Integers</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/subarrays-with-k-different-integers/</t>
-  </si>
-  <si>
-    <t>Build an Array With Stack Operations</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/build-an-array-with-stack-operations/</t>
-  </si>
-  <si>
-    <t>Design Circular Deque</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/design-circular-deque/</t>
+    <t>Maximum Nesting Depth</t>
+  </si>
+  <si>
+    <t>Find Winner of Circular Game</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/maximum-nesting-depth-of-the-parentheses/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/find-the-winner-of-the-circular-game/</t>
+  </si>
+  <si>
+    <t>Queue / Circular</t>
+  </si>
+  <si>
+    <t>Stack / Counter</t>
+  </si>
+  <si>
+    <t>Queue Reconstruction by Height</t>
+  </si>
+  <si>
+    <t>Remove All Adjacent Duplicates II</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/queue-reconstruction-by-height/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/remove-all-adjacent-duplicates-in-string-ii/</t>
+  </si>
+  <si>
+    <t>Traversal</t>
   </si>
   <si>
     <t>HashMap</t>
   </si>
   <si>
+    <t>TCS, Infosys, Barclays</t>
+  </si>
+  <si>
     <t>Google, Amazon</t>
   </si>
   <si>
+    <t>Search Element in Linked List</t>
+  </si>
+  <si>
     <t>Max Consecutive Ones III</t>
   </si>
   <si>
+    <t>https://www.hackerrank.com/challenges/compare-two-linked-lists/problem</t>
+  </si>
+  <si>
     <t>https://leetcode.com/problems/max-consecutive-ones-iii/</t>
   </si>
   <si>
-    <t>Traversal</t>
-  </si>
-  <si>
-    <t>TCS, Infosys, Barclays</t>
-  </si>
-  <si>
-    <t>Search Element in Linked List</t>
-  </si>
-  <si>
-    <t>https://www.hackerrank.com/challenges/compare-two-linked-lists/problem</t>
-  </si>
-  <si>
-    <t>Find Winner of Circular Game</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/find-the-winner-of-the-circular-game/</t>
-  </si>
-  <si>
-    <t>Final Prices With Discount</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/final-prices-with-a-special-discount-in-a-shop/</t>
-  </si>
-  <si>
-    <t>Queue / Circular</t>
-  </si>
-  <si>
-    <t>Queue Reconstruction by Height</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/queue-reconstruction-by-height/</t>
+    <t>Greedy + Queue</t>
+  </si>
+  <si>
+    <t>Shortest Distance to Character</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/shortest-distance-to-a-character/</t>
+  </si>
+  <si>
+    <t>Simplify Path</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/simplify-path/</t>
+  </si>
+  <si>
+    <t>BFS/Queue</t>
+  </si>
+  <si>
+    <t>Count Students Doing Homework at Time</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/number-of-students-doing-homework-at-a-given-time/</t>
   </si>
   <si>
     <t>Linear Search</t>
@@ -426,31 +474,18 @@
     <t>Insert Node at Beginning / End</t>
   </si>
   <si>
-    <t>https://www.hackerrank.com/challenges/insert-a-node-at-the-head-of-a-linked-list/problem
-https://www.hackerrank.com/challenges/insert-a-node-at-the-tail-of-a-linked-list/problem</t>
-  </si>
-  <si>
-    <t>Monotonic Stack</t>
-  </si>
-  <si>
-    <t>Remove All Adjacent Duplicates</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/remove-all-adjacent-duplicates-in-string/</t>
-  </si>
-  <si>
-    <t>Greedy + Queue</t>
-  </si>
-  <si>
-    <t>Shortest Distance to Character</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/shortest-distance-to-a-character/</t>
+    <t>https://www.hackerrank.com/challenges/insert-a-node-at-the-head-of-a-linked-list/problem ; https://www.hackerrank.com/challenges/insert-a-node-at-the-tail-of-a-linked-list/problem</t>
+  </si>
+  <si>
+    <t>Evaluate Reverse Polish Notation</t>
   </si>
   <si>
     <t>Basic Pointer Manipulation</t>
   </si>
   <si>
+    <t>https://leetcode.com/problems/evaluate-reverse-polish-notation/</t>
+  </si>
+  <si>
     <t>Almost all (basic screening)</t>
   </si>
   <si>
@@ -460,19 +495,34 @@
     <t>https://www.hackerrank.com/challenges/print-the-elements-of-a-linked-list-in-reverse/problem</t>
   </si>
   <si>
-    <t>BFS/Queue</t>
-  </si>
-  <si>
-    <t>Maximum Nesting Depth</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/maximum-nesting-depth-of-the-parentheses/</t>
-  </si>
-  <si>
-    <t>Count Students Doing Homework at Time</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/number-of-students-doing-homework-at-a-given-time/</t>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>Ping Counter (Recent Calls Variant)</t>
+  </si>
+  <si>
+    <t>Binary Tree Level Order Traversal</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/binary-tree-level-order-traversal/</t>
+  </si>
+  <si>
+    <t>Stack Evaluation</t>
+  </si>
+  <si>
+    <t>Daily Temperatures</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/daily-temperatures/</t>
+  </si>
+  <si>
+    <t>BFS</t>
+  </si>
+  <si>
+    <t>Rotting Oranges</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/rotting-oranges/</t>
   </si>
   <si>
     <t>Recursion / Stack</t>
@@ -481,37 +531,31 @@
     <t>Find Nth Node from Beginning</t>
   </si>
   <si>
-    <t>Basic</t>
-  </si>
-  <si>
-    <t>Stack / Counter</t>
+    <t>Next Greater Element II</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/next-greater-element-ii/</t>
   </si>
   <si>
     <t>Traversal / Counter</t>
   </si>
   <si>
-    <t>Ping Counter (Recent Calls Variant)</t>
-  </si>
-  <si>
     <t>Infosys, Capgemini</t>
   </si>
   <si>
-    <t>Remove All Adjacent Duplicates II</t>
+    <t>Multi-source BFS</t>
+  </si>
+  <si>
+    <t>Open the Lock</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/open-the-lock/</t>
   </si>
   <si>
     <t>Check if Linked List is Empty</t>
   </si>
   <si>
-    <t>https://leetcode.com/problems/remove-all-adjacent-duplicates-in-string-ii/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   </t>
-  </si>
-  <si>
-    <t>Binary Tree Level Order Traversal</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/binary-tree-level-order-traversal/</t>
+    <t>NA</t>
   </si>
   <si>
     <t>Basic Check</t>
@@ -523,13 +567,31 @@
     <t>Count Occurrences of a Value</t>
   </si>
   <si>
+    <t>Online Stock Span</t>
+  </si>
+  <si>
     <t>https://www.hackerrank.com/challenges/delete-a-node-from-a-linked-list/problem</t>
   </si>
   <si>
-    <t>Simplify Path</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/simplify-path/</t>
+    <t>https://leetcode.com/problems/online-stock-span/</t>
+  </si>
+  <si>
+    <t>Number of Islands</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/number-of-islands/</t>
+  </si>
+  <si>
+    <t>Asteroid Collision</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/asteroid-collision/</t>
+  </si>
+  <si>
+    <t>Walls and Gates</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/walls-and-gates/</t>
   </si>
   <si>
     <t>TCS, Accenture</t>
@@ -538,9 +600,6 @@
     <t>Convert Array to Linked List</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Construction</t>
   </si>
   <si>
@@ -553,10 +612,31 @@
     <t>https://leetcode.com/problems/remove-nth-node-from-end-of-list/</t>
   </si>
   <si>
-    <t>Evaluate Reverse Polish Notation</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/evaluate-reverse-polish-notation/</t>
+    <t>Decode String</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/decode-string/</t>
+  </si>
+  <si>
+    <t>Perfect Squares</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/perfect-squares/</t>
+  </si>
+  <si>
+    <t>Stack + Recursion</t>
+  </si>
+  <si>
+    <t>Remove K Digits</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/remove-k-digits/</t>
+  </si>
+  <si>
+    <t>Course Schedule</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/course-schedule/</t>
   </si>
   <si>
     <t>Two Pointer (Gap Technique)</t>
@@ -571,27 +651,39 @@
     <t>https://leetcode.com/problems/linked-list-cycle-ii/</t>
   </si>
   <si>
-    <t>BFS</t>
-  </si>
-  <si>
-    <t>Rotting Oranges</t>
-  </si>
-  <si>
-    <t>Stack Evaluation</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/rotting-oranges/</t>
-  </si>
-  <si>
-    <t>Daily Temperatures</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/daily-temperatures/</t>
+    <t>Monotonic Stack (Greedy)</t>
+  </si>
+  <si>
+    <t>Largest Rectangle in Histogram</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/largest-rectangle-in-histogram/</t>
+  </si>
+  <si>
+    <t>Topological Sort</t>
+  </si>
+  <si>
+    <t>Course Schedule II</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/course-schedule-ii/</t>
+  </si>
+  <si>
+    <t>Basic Calculator II</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/basic-calculator-ii/</t>
   </si>
   <si>
     <t>Fast &amp; Slow Pointer + Entry Point Logic</t>
   </si>
   <si>
+    <t>Jump Game II</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/jump-game-ii/</t>
+  </si>
+  <si>
     <t>Google, Uber, Amazon</t>
   </si>
   <si>
@@ -601,49 +693,52 @@
     <t>https://leetcode.com/problems/intersection-of-two-linked-lists/</t>
   </si>
   <si>
-    <t>Multi-source BFS</t>
-  </si>
-  <si>
-    <t>Open the Lock</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/open-the-lock/</t>
-  </si>
-  <si>
-    <t>Next Greater Element II</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/next-greater-element-ii/</t>
-  </si>
-  <si>
-    <t>Number of Islands</t>
+    <t>Score of Parentheses</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/score-of-parentheses/</t>
+  </si>
+  <si>
+    <t>BFS / Greedy</t>
+  </si>
+  <si>
+    <t>K Closest Points to Origin</t>
   </si>
   <si>
     <t>Two Pointer Switching</t>
   </si>
   <si>
-    <t>https://leetcode.com/problems/number-of-islands/</t>
+    <t>https://leetcode.com/problems/k-closest-points-to-origin/</t>
   </si>
   <si>
     <t>Microsoft, Amazon, Goldman Sachs</t>
   </si>
   <si>
+    <t>Validate Stack Sequences</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/validate-stack-sequences/</t>
+  </si>
+  <si>
     <t>Palindrome Linked List</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/palindrome-linked-list/</t>
   </si>
   <si>
-    <t>Online Stock Span</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/online-stock-span/</t>
-  </si>
-  <si>
-    <t>Walls and Gates</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/walls-and-gates/</t>
+    <t>Heap/Queue</t>
+  </si>
+  <si>
+    <t>Priority Queue</t>
+  </si>
+  <si>
+    <t>Largest Rectangle in Histogram (Advanced revisit)</t>
+  </si>
+  <si>
+    <t>Maximal Rectangle</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/maximal-rectangle/</t>
   </si>
   <si>
     <t>Reverse Half + Two Pointer</t>
@@ -658,40 +753,67 @@
     <t>https://leetcode.com/problems/add-two-numbers/</t>
   </si>
   <si>
-    <t>Perfect Squares</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/perfect-squares/</t>
-  </si>
-  <si>
-    <t>Asteroid Collision</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/asteroid-collision/</t>
+    <t>Minimum Window Substring</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/minimum-window-substring/</t>
+  </si>
+  <si>
+    <t>Stack + Histogram</t>
+  </si>
+  <si>
+    <t>Basic Calculator</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/basic-calculator/</t>
+  </si>
+  <si>
+    <t>Stack + Expression Parsing</t>
   </si>
   <si>
     <t>Digit-wise Addition + Carry</t>
   </si>
   <si>
+    <t>Basic Calculator III</t>
+  </si>
+  <si>
+    <t>Queue/Map</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/basic-calculator-iii/</t>
+  </si>
+  <si>
     <t>Reverse Linked List II (Between positions m and n)</t>
   </si>
   <si>
+    <t>Shortest Path in Binary Matrix</t>
+  </si>
+  <si>
     <t>https://leetcode.com/problems/reverse-linked-list-ii/</t>
   </si>
   <si>
-    <t>Course Schedule</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/course-schedule/</t>
-  </si>
-  <si>
-    <t>Decode String</t>
+    <t>https://leetcode.com/problems/shortest-path-in-binary-matrix/</t>
+  </si>
+  <si>
+    <t>Stack + Parsing</t>
+  </si>
+  <si>
+    <t>Alien Dictionary</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/alien-dictionary/</t>
+  </si>
+  <si>
+    <t>Stack/Deque</t>
   </si>
   <si>
     <t>Sublist Reversal</t>
   </si>
   <si>
-    <t>https://leetcode.com/problems/decode-string/</t>
+    <t>Word Ladder</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/word-ladder/</t>
   </si>
   <si>
     <t>Reorder List (L0 → Ln → L1 → Ln-1)</t>
@@ -700,159 +822,54 @@
     <t>https://leetcode.com/problems/reorder-list/</t>
   </si>
   <si>
-    <t>Topological Sort</t>
-  </si>
-  <si>
-    <t>Course Schedule II</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/course-schedule-ii/</t>
-  </si>
-  <si>
-    <t>Stack + Recursion</t>
-  </si>
-  <si>
     <t>Fast/Slow + Reverse + Merge</t>
   </si>
   <si>
-    <t>Remove K Digits</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/remove-k-digits/</t>
-  </si>
-  <si>
     <t>Partition List (based on value x)</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/partition-list/</t>
   </si>
   <si>
-    <t>Jump Game II</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/jump-game-ii/</t>
-  </si>
-  <si>
-    <t>Monotonic Stack (Greedy)</t>
-  </si>
-  <si>
-    <t>Largest Rectangle in Histogram</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/largest-rectangle-in-histogram/</t>
-  </si>
-  <si>
     <t>Two Lists / Dummy Nodes</t>
   </si>
   <si>
     <t>Sort Linked List (Merge Sort)</t>
   </si>
   <si>
-    <t>BFS / Greedy</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/sort-list/</t>
   </si>
   <si>
-    <t>K Closest Points to Origin</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/k-closest-points-to-origin/</t>
-  </si>
-  <si>
-    <t>Basic Calculator II</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/basic-calculator-ii/</t>
-  </si>
-  <si>
     <t>Merge Sort</t>
   </si>
   <si>
-    <t>Heap/Queue</t>
-  </si>
-  <si>
-    <t>Priority Queue</t>
-  </si>
-  <si>
     <t>Swap Nodes in Pairs</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/swap-nodes-in-pairs/</t>
   </si>
   <si>
-    <t>Score of Parentheses</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/score-of-parentheses/</t>
-  </si>
-  <si>
     <t>Iteration / Pair Manipulation</t>
   </si>
   <si>
     <t>Microsoft, Amazon</t>
   </si>
   <si>
-    <t>Minimum Window Substring</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/minimum-window-substring/</t>
-  </si>
-  <si>
     <t>Reverse Nodes in K-Group</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/reverse-nodes-in-k-group/</t>
   </si>
   <si>
-    <t>Validate Stack Sequences</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/validate-stack-sequences/</t>
-  </si>
-  <si>
-    <t>Queue/Map</t>
-  </si>
-  <si>
-    <t>Shortest Path in Binary Matrix</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/shortest-path-in-binary-matrix/</t>
-  </si>
-  <si>
-    <t>Largest Rectangle in Histogram (Advanced revisit)</t>
-  </si>
-  <si>
     <t>K-group Reversal</t>
   </si>
   <si>
     <t>Merge K Sorted Linked Lists</t>
   </si>
   <si>
-    <t>Maximal Rectangle</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/merge-k-sorted-lists/</t>
   </si>
   <si>
-    <t>https://leetcode.com/problems/maximal-rectangle/</t>
-  </si>
-  <si>
-    <t>Alien Dictionary</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/alien-dictionary/</t>
-  </si>
-  <si>
-    <t>Stack + Histogram</t>
-  </si>
-  <si>
-    <t>Basic Calculator</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/basic-calculator/</t>
-  </si>
-  <si>
     <t>Heap / Divide &amp; Conquer</t>
   </si>
   <si>
@@ -862,39 +879,18 @@
     <t>Copy List with Random Pointer</t>
   </si>
   <si>
-    <t>Stack + Expression Parsing</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/copy-list-with-random-pointer/</t>
   </si>
   <si>
-    <t>Word Ladder</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/word-ladder/</t>
-  </si>
-  <si>
-    <t>Basic Calculator III</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/basic-calculator-iii/</t>
-  </si>
-  <si>
-    <t>Stack + Parsing</t>
-  </si>
-  <si>
     <t>HashMap / Interleaving Nodes</t>
   </si>
   <si>
-    <t>Linked List + Heap</t>
+    <t>Linked List + Random Pointer</t>
   </si>
   <si>
     <t>Amazon, Microsoft, Google</t>
   </si>
   <si>
-    <t>Stack/Deque</t>
-  </si>
-  <si>
     <t>LRU Cache (Using LinkedList + HashMap)</t>
   </si>
   <si>
@@ -917,6 +913,45 @@
   </si>
   <si>
     <t>Doubly Linked List</t>
+  </si>
+  <si>
+    <t>Odd Even Linked List</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/odd-even-linked-list/</t>
+  </si>
+  <si>
+    <t>Pointer Rewiring</t>
+  </si>
+  <si>
+    <t>Rotate List</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/rotate-list/</t>
+  </si>
+  <si>
+    <t>Length + Tail Connection</t>
+  </si>
+  <si>
+    <t>Common pointer-manipulation interview problem</t>
+  </si>
+  <si>
+    <t>Design Browser History</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/design-browser-history/</t>
+  </si>
+  <si>
+    <t>Common design / DLL interview problem</t>
+  </si>
+  <si>
+    <t>LFU Cache</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/lfu-cache/</t>
+  </si>
+  <si>
+    <t>Senior interview follow-up to LRU Cache</t>
   </si>
 </sst>
 </file>
@@ -940,18 +975,19 @@
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
-      <color rgb="FF0000FF"/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
     </font>
     <font>
       <u/>
       <color rgb="FF0000FF"/>
     </font>
     <font>
-      <b/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="2">
@@ -968,20 +1004,19 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1236,611 +1271,685 @@
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B30" s="4" t="s">
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
+      <c r="E35" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
     <row r="36" ht="15.75" customHeight="1"/>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
@@ -2805,7 +2914,6 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B2"/>
@@ -2817,27 +2925,30 @@
     <hyperlink r:id="rId7" ref="B8"/>
     <hyperlink r:id="rId8" ref="B9"/>
     <hyperlink r:id="rId9" ref="B10"/>
-    <hyperlink r:id="rId10" ref="B11"/>
-    <hyperlink r:id="rId11" ref="B12"/>
-    <hyperlink r:id="rId12" ref="B13"/>
-    <hyperlink r:id="rId13" ref="B15"/>
-    <hyperlink r:id="rId14" ref="B17"/>
-    <hyperlink r:id="rId15" ref="B18"/>
-    <hyperlink r:id="rId16" ref="B19"/>
-    <hyperlink r:id="rId17" ref="B20"/>
-    <hyperlink r:id="rId18" ref="B21"/>
-    <hyperlink r:id="rId19" ref="B22"/>
-    <hyperlink r:id="rId20" ref="B23"/>
-    <hyperlink r:id="rId21" ref="B24"/>
-    <hyperlink r:id="rId22" ref="B25"/>
-    <hyperlink r:id="rId23" ref="B26"/>
-    <hyperlink r:id="rId24" ref="B27"/>
-    <hyperlink r:id="rId25" ref="B28"/>
-    <hyperlink r:id="rId26" ref="B29"/>
-    <hyperlink r:id="rId27" ref="B30"/>
-    <hyperlink r:id="rId28" ref="B31"/>
+    <hyperlink r:id="rId10" ref="B12"/>
+    <hyperlink r:id="rId11" ref="B13"/>
+    <hyperlink r:id="rId12" ref="B15"/>
+    <hyperlink r:id="rId13" ref="B17"/>
+    <hyperlink r:id="rId14" ref="B18"/>
+    <hyperlink r:id="rId15" ref="B19"/>
+    <hyperlink r:id="rId16" ref="B20"/>
+    <hyperlink r:id="rId17" ref="B21"/>
+    <hyperlink r:id="rId18" ref="B22"/>
+    <hyperlink r:id="rId19" ref="B23"/>
+    <hyperlink r:id="rId20" ref="B24"/>
+    <hyperlink r:id="rId21" ref="B25"/>
+    <hyperlink r:id="rId22" ref="B26"/>
+    <hyperlink r:id="rId23" ref="B27"/>
+    <hyperlink r:id="rId24" ref="B28"/>
+    <hyperlink r:id="rId25" ref="B29"/>
+    <hyperlink r:id="rId26" ref="B30"/>
+    <hyperlink r:id="rId27" ref="B31"/>
+    <hyperlink r:id="rId28" ref="B32"/>
+    <hyperlink r:id="rId29" ref="B33"/>
+    <hyperlink r:id="rId30" ref="B34"/>
+    <hyperlink r:id="rId31" ref="B35"/>
   </hyperlinks>
-  <drawing r:id="rId29"/>
+  <drawing r:id="rId32"/>
 </worksheet>
 </file>
 
@@ -2881,599 +2992,599 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="E27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -4519,602 +4630,602 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -6160,142 +6271,142 @@
     </row>
     <row r="2" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1"/>
